--- a/MainTop/ink statistic/ink statistic.xlsx
+++ b/MainTop/ink statistic/ink statistic.xlsx
@@ -5,41 +5,35 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\ink statistic\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\ink statistic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF528B88-230D-4BD1-98F9-7E190B733502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DADE85F9-CB52-46AD-87AD-0F05917FBE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="total" sheetId="3" r:id="rId1"/>
-    <sheet name="Лист1" sheetId="1" r:id="rId2"/>
-    <sheet name="Лист2" sheetId="2" r:id="rId3"/>
-    <sheet name="Лист3" sheetId="4" r:id="rId4"/>
-    <sheet name="Лист4" sheetId="5" r:id="rId5"/>
-    <sheet name="Лист5" sheetId="6" r:id="rId6"/>
+    <sheet name="Лист6" sheetId="7" r:id="rId2"/>
+    <sheet name="Лист1" sheetId="1" r:id="rId3"/>
+    <sheet name="Лист2" sheetId="2" r:id="rId4"/>
+    <sheet name="Лист3" sheetId="4" r:id="rId5"/>
+    <sheet name="Лист4" sheetId="5" r:id="rId6"/>
+    <sheet name="Лист5" sheetId="6" r:id="rId7"/>
+    <sheet name="остатки 12.05.2026" sheetId="8" r:id="rId8"/>
+    <sheet name="спрос" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="28">
   <si>
     <t>k</t>
   </si>
@@ -69,6 +63,60 @@
   </si>
   <si>
     <t>наши рачеты на 1 рулон уходит</t>
+  </si>
+  <si>
+    <t>powder</t>
+  </si>
+  <si>
+    <t>film</t>
+  </si>
+  <si>
+    <t>clean solution</t>
+  </si>
+  <si>
+    <t>скотч металл</t>
+  </si>
+  <si>
+    <t>остатки</t>
+  </si>
+  <si>
+    <t>шт</t>
+  </si>
+  <si>
+    <t>расход</t>
+  </si>
+  <si>
+    <t>в пути</t>
+  </si>
+  <si>
+    <t>punky monkey ВБ</t>
+  </si>
+  <si>
+    <t>amazing pics</t>
+  </si>
+  <si>
+    <t>amazing pics OZON</t>
+  </si>
+  <si>
+    <t>punky monkey OZON</t>
+  </si>
+  <si>
+    <t>punky monkey stickers OZON</t>
+  </si>
+  <si>
+    <t>итого</t>
+  </si>
+  <si>
+    <t>спрос в мес</t>
+  </si>
+  <si>
+    <t>количество расхода в месяц</t>
+  </si>
+  <si>
+    <t>остатки итого</t>
+  </si>
+  <si>
+    <t>купить на X месяцев</t>
   </si>
 </sst>
 </file>
@@ -84,15 +132,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -100,12 +154,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -386,14 +462,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1417238C-D5E6-459E-9CEF-E017A45F1F58}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" customWidth="1"/>
     <col min="7" max="7" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>5</v>
       </c>
@@ -409,8 +487,11 @@
       <c r="G1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -433,11 +514,15 @@
         <v>600</v>
       </c>
       <c r="G2">
-        <f>G6*B2*B6</f>
-        <v>69.204424000000003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <f>G6*B2</f>
+        <v>91.4</v>
+      </c>
+      <c r="H2">
+        <f>ROUND(G2/1000,2)</f>
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -450,11 +535,15 @@
         <v>4</v>
       </c>
       <c r="G3">
-        <f>G6*B3*B6</f>
-        <v>69.583004000000003</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <f>G6*B3</f>
+        <v>91.899999999999991</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H6" si="1">ROUND(G3/1000,2)</f>
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -467,11 +556,15 @@
         <v>7</v>
       </c>
       <c r="G4">
-        <f>G6*B6*B4</f>
-        <v>141.664636</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <f>G6*B4</f>
+        <v>187.10000000000002</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="1"/>
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -484,11 +577,15 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <f>G6*B6*B5</f>
-        <v>178.53832800000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <f>G6*B5</f>
+        <v>235.8</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -501,17 +598,44 @@
         <v>76</v>
       </c>
       <c r="G6">
+        <f>2500</f>
         <v>2500</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B7">
-        <f>SUM(B2:B6)</f>
-        <v>0.99964000000000008</v>
-      </c>
-      <c r="G7">
-        <f>SUM(G2:G6)</f>
-        <v>2958.9903920000002</v>
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -520,6 +644,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE49E650-0387-4205-894C-7D214F736D44}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -575,7 +708,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAA15FB0-ECB9-47D4-BE04-0C95B3A3395A}">
   <dimension ref="A2:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -631,7 +764,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC645C2F-8595-4FFF-BC02-593D2927B4F4}">
   <dimension ref="A2:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -687,7 +820,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39729167-92B2-489F-86B0-C0A74BA0E763}">
   <dimension ref="A2:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -743,7 +876,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36F4CF9D-614D-40DF-AA98-C8C3D39CF332}">
   <dimension ref="A2:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -797,4 +930,413 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D0C29C9-9A8E-498E-98C9-49B6E2A56B74}">
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" customWidth="1"/>
+    <col min="9" max="9" width="8.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <f>total!H2</f>
+        <v>0.09</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <f>B2+D2</f>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>30000</v>
+      </c>
+      <c r="G2">
+        <f>ROUNDUP(C2*F2/1000,0)</f>
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <f>G2*H2-E2</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <f>total!H3</f>
+        <v>0.09</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <f t="shared" ref="E3:E10" si="0">B3+D3</f>
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>30000</v>
+      </c>
+      <c r="G3">
+        <f>ROUNDUP(C3*F3/1000,0)</f>
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <f>G3*H3-E3</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <f>total!H4</f>
+        <v>0.19</v>
+      </c>
+      <c r="E4" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="F4">
+        <v>30000</v>
+      </c>
+      <c r="G4">
+        <f>ROUNDUP(C4*F4/1000,0)</f>
+        <v>6</v>
+      </c>
+      <c r="H4">
+        <v>4</v>
+      </c>
+      <c r="I4">
+        <f>G4*H4-E4</f>
+        <v>15</v>
+      </c>
+      <c r="M4">
+        <f>SUM(I2:I6)</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <f>total!H5</f>
+        <v>0.24</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>30000</v>
+      </c>
+      <c r="G5">
+        <f>ROUNDUP(C5*F5/1000,0)</f>
+        <v>8</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <f>G5*H5-E5</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>169</v>
+      </c>
+      <c r="C6">
+        <f>total!H6</f>
+        <v>2.5</v>
+      </c>
+      <c r="E6" s="1">
+        <f t="shared" si="0"/>
+        <v>169</v>
+      </c>
+      <c r="F6">
+        <v>30000</v>
+      </c>
+      <c r="G6">
+        <f>ROUNDUP(C6*F6/1000,0)</f>
+        <v>75</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <f>G6*H6-E6</f>
+        <v>131</v>
+      </c>
+      <c r="K6">
+        <f>(1100+540)*85</f>
+        <v>139400</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>100</v>
+      </c>
+      <c r="C7">
+        <f>total!H7</f>
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>120</v>
+      </c>
+      <c r="E7" s="1">
+        <f t="shared" si="0"/>
+        <v>220</v>
+      </c>
+      <c r="F7">
+        <v>30000</v>
+      </c>
+      <c r="G7">
+        <f>C7*F7/1000</f>
+        <v>120</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <f>G7*H7-E7</f>
+        <v>260</v>
+      </c>
+      <c r="K7">
+        <f>I7*8*85</f>
+        <v>176800</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>22</v>
+      </c>
+      <c r="C8">
+        <f>total!H8</f>
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>36</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="F8">
+        <v>30000</v>
+      </c>
+      <c r="G8">
+        <f>C8*F8/1000</f>
+        <v>30</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <f>G8*H8-E8</f>
+        <v>62</v>
+      </c>
+      <c r="K8">
+        <f>I8*3800</f>
+        <v>235600</v>
+      </c>
+      <c r="L8">
+        <f>SUM(K6:K8)</f>
+        <v>551800</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
+        <v>25</v>
+      </c>
+      <c r="C9">
+        <f>total!H9</f>
+        <v>0.25</v>
+      </c>
+      <c r="E9" s="1">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="F9">
+        <v>30000</v>
+      </c>
+      <c r="G9">
+        <f>C9*F9/1000</f>
+        <v>7.5</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9">
+        <f>G9*H9-E9</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <f>total!H10</f>
+        <v>0.25</v>
+      </c>
+      <c r="E10" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>30000</v>
+      </c>
+      <c r="G10">
+        <f>C10*F10/1000</f>
+        <v>7.5</v>
+      </c>
+      <c r="H10">
+        <v>4</v>
+      </c>
+      <c r="I10">
+        <f>G10*H10-E10</f>
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{226A9FAA-9B28-4465-A0CA-F334D704BDBB}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" customWidth="1"/>
+    <col min="5" max="5" width="27.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2000</v>
+      </c>
+      <c r="B2">
+        <v>10400</v>
+      </c>
+      <c r="C2">
+        <v>3000</v>
+      </c>
+      <c r="D2">
+        <v>870</v>
+      </c>
+      <c r="E2">
+        <v>1400</v>
+      </c>
+      <c r="F2">
+        <f>SUM(A2:E2)</f>
+        <v>17670</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/MainTop/ink statistic/ink statistic.xlsx
+++ b/MainTop/ink statistic/ink statistic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\ink statistic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DADE85F9-CB52-46AD-87AD-0F05917FBE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B370DB41-4893-45EC-BDD6-2D616BC2EE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -934,7 +934,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D0C29C9-9A8E-498E-98C9-49B6E2A56B74}">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
@@ -1002,7 +1002,7 @@
         <v>4</v>
       </c>
       <c r="I2">
-        <f>G2*H2-E2</f>
+        <f t="shared" ref="I2:I10" si="0">G2*H2-E2</f>
         <v>7</v>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="1">
-        <f t="shared" ref="E3:E10" si="0">B3+D3</f>
+        <f t="shared" ref="E3:E10" si="1">B3+D3</f>
         <v>6</v>
       </c>
       <c r="F3">
@@ -1035,7 +1035,7 @@
         <v>4</v>
       </c>
       <c r="I3">
-        <f>G3*H3-E3</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
         <v>0.19</v>
       </c>
       <c r="E4" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="F4">
@@ -1065,7 +1065,7 @@
         <v>4</v>
       </c>
       <c r="I4">
-        <f>G4*H4-E4</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="M4">
@@ -1088,7 +1088,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="F5">
@@ -1102,7 +1102,7 @@
         <v>4</v>
       </c>
       <c r="I5">
-        <f>G5*H5-E5</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
         <v>2.5</v>
       </c>
       <c r="E6" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>169</v>
       </c>
       <c r="F6">
@@ -1132,7 +1132,7 @@
         <v>4</v>
       </c>
       <c r="I6">
-        <f>G6*H6-E6</f>
+        <f t="shared" si="0"/>
         <v>131</v>
       </c>
       <c r="K6">
@@ -1155,7 +1155,7 @@
         <v>120</v>
       </c>
       <c r="E7" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>220</v>
       </c>
       <c r="F7">
@@ -1169,7 +1169,7 @@
         <v>4</v>
       </c>
       <c r="I7">
-        <f>G7*H7-E7</f>
+        <f t="shared" si="0"/>
         <v>260</v>
       </c>
       <c r="K7">
@@ -1192,7 +1192,7 @@
         <v>36</v>
       </c>
       <c r="E8" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
       <c r="F8">
@@ -1206,7 +1206,7 @@
         <v>4</v>
       </c>
       <c r="I8">
-        <f>G8*H8-E8</f>
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
       <c r="K8">
@@ -1230,7 +1230,7 @@
         <v>0.25</v>
       </c>
       <c r="E9" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="F9">
@@ -1244,7 +1244,7 @@
         <v>4</v>
       </c>
       <c r="I9">
-        <f>G9*H9-E9</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
         <v>0.25</v>
       </c>
       <c r="E10" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F10">
@@ -1274,8 +1274,14 @@
         <v>4</v>
       </c>
       <c r="I10">
-        <f>G10*H10-E10</f>
+        <f t="shared" si="0"/>
         <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <f>62*3800</f>
+        <v>235600</v>
       </c>
     </row>
   </sheetData>

--- a/MainTop/ink statistic/ink statistic.xlsx
+++ b/MainTop/ink statistic/ink statistic.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\ink statistic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B370DB41-4893-45EC-BDD6-2D616BC2EE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6644C1B-EC90-4284-8E2F-5D8668F14B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="total" sheetId="3" r:id="rId1"/>
-    <sheet name="Лист6" sheetId="7" r:id="rId2"/>
-    <sheet name="Лист1" sheetId="1" r:id="rId3"/>
-    <sheet name="Лист2" sheetId="2" r:id="rId4"/>
-    <sheet name="Лист3" sheetId="4" r:id="rId5"/>
-    <sheet name="Лист4" sheetId="5" r:id="rId6"/>
-    <sheet name="Лист5" sheetId="6" r:id="rId7"/>
-    <sheet name="остатки 12.05.2026" sheetId="8" r:id="rId8"/>
-    <sheet name="спрос" sheetId="9" r:id="rId9"/>
+    <sheet name="Лист1" sheetId="1" r:id="rId2"/>
+    <sheet name="Лист2" sheetId="2" r:id="rId3"/>
+    <sheet name="Лист3" sheetId="4" r:id="rId4"/>
+    <sheet name="Лист4" sheetId="5" r:id="rId5"/>
+    <sheet name="Лист5" sheetId="6" r:id="rId6"/>
+    <sheet name="остатки 12.05.2026" sheetId="8" r:id="rId7"/>
+    <sheet name="спрос" sheetId="9" r:id="rId8"/>
+    <sheet name="остатки" sheetId="10" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="181029" iterateDelta="1E-4"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="36">
   <si>
     <t>k</t>
   </si>
@@ -117,13 +117,37 @@
   </si>
   <si>
     <t>купить на X месяцев</t>
+  </si>
+  <si>
+    <t>краски</t>
+  </si>
+  <si>
+    <t>коробка 230х190х190</t>
+  </si>
+  <si>
+    <t>пакеты 22х30</t>
+  </si>
+  <si>
+    <t>пакеты 18х25</t>
+  </si>
+  <si>
+    <t>хватит на мес</t>
+  </si>
+  <si>
+    <t>коробка 310х240х200</t>
+  </si>
+  <si>
+    <t>коробка 310х240х100</t>
+  </si>
+  <si>
+    <t>заказать на Х месяцев</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,8 +155,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -142,6 +175,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -173,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -182,6 +233,24 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -644,15 +713,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE49E650-0387-4205-894C-7D214F736D44}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -708,7 +768,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAA15FB0-ECB9-47D4-BE04-0C95B3A3395A}">
   <dimension ref="A2:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -764,7 +824,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC645C2F-8595-4FFF-BC02-593D2927B4F4}">
   <dimension ref="A2:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -820,7 +880,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39729167-92B2-489F-86B0-C0A74BA0E763}">
   <dimension ref="A2:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -876,7 +936,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36F4CF9D-614D-40DF-AA98-C8C3D39CF332}">
   <dimension ref="A2:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -932,7 +992,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D0C29C9-9A8E-498E-98C9-49B6E2A56B74}">
   <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1289,7 +1349,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{226A9FAA-9B28-4465-A0CA-F334D704BDBB}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1345,4 +1405,500 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5752FFBB-2BA0-4D25-94B6-08B45A9708D1}">
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.42578125" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
+        <v>30000</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+    </row>
+    <row r="3" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="5"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="C4" s="5">
+        <v>4</v>
+      </c>
+      <c r="D4" s="7">
+        <v>7</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="1">
+        <f t="shared" ref="F4:F8" si="0">SUM(C4:E4)</f>
+        <v>11</v>
+      </c>
+      <c r="G4" s="5">
+        <f>A2</f>
+        <v>30000</v>
+      </c>
+      <c r="H4" s="5">
+        <f t="shared" ref="H4:H9" si="1">ROUNDUP(B4*G4/1000,0)</f>
+        <v>3</v>
+      </c>
+      <c r="I4" s="5">
+        <f>ROUNDUP(F4/H4,1)</f>
+        <v>3.7</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5">
+        <f>H4*J4</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="C5" s="5">
+        <v>4</v>
+      </c>
+      <c r="D5" s="7">
+        <v>7</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="1">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="G5" s="5">
+        <f>A2</f>
+        <v>30000</v>
+      </c>
+      <c r="H5" s="5">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I12" si="2">ROUNDUP(F5/H5,1)</f>
+        <v>3.7</v>
+      </c>
+      <c r="J5" s="5">
+        <v>2</v>
+      </c>
+      <c r="K5" s="5">
+        <f t="shared" ref="K5:K12" si="3">H5*J5</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0.19</v>
+      </c>
+      <c r="C6" s="5">
+        <v>6</v>
+      </c>
+      <c r="D6" s="7">
+        <v>15</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="G6" s="5">
+        <f>A2</f>
+        <v>30000</v>
+      </c>
+      <c r="H6" s="5">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="2"/>
+        <v>3.5</v>
+      </c>
+      <c r="J6" s="5">
+        <v>2</v>
+      </c>
+      <c r="K6" s="5">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0.24</v>
+      </c>
+      <c r="C7" s="5">
+        <v>9</v>
+      </c>
+      <c r="D7" s="7">
+        <v>21</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="G7" s="5">
+        <f>A2</f>
+        <v>30000</v>
+      </c>
+      <c r="H7" s="5">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="2"/>
+        <v>3.8000000000000003</v>
+      </c>
+      <c r="J7" s="5">
+        <v>2</v>
+      </c>
+      <c r="K7" s="5">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="C8" s="5">
+        <v>130</v>
+      </c>
+      <c r="D8" s="7">
+        <v>130</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="1">
+        <f t="shared" si="0"/>
+        <v>260</v>
+      </c>
+      <c r="G8" s="5">
+        <f>A2</f>
+        <v>30000</v>
+      </c>
+      <c r="H8" s="5">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="2"/>
+        <v>3.5</v>
+      </c>
+      <c r="J8" s="5">
+        <v>2</v>
+      </c>
+      <c r="K8" s="5">
+        <f t="shared" si="3"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5">
+        <v>4</v>
+      </c>
+      <c r="C9" s="5">
+        <v>100</v>
+      </c>
+      <c r="D9" s="8">
+        <v>120</v>
+      </c>
+      <c r="E9" s="8">
+        <v>260</v>
+      </c>
+      <c r="F9" s="1">
+        <f>SUM(C9:E9)</f>
+        <v>480</v>
+      </c>
+      <c r="G9" s="5">
+        <f>A2</f>
+        <v>30000</v>
+      </c>
+      <c r="H9" s="5">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="J9" s="5">
+        <v>2</v>
+      </c>
+      <c r="K9" s="5">
+        <f t="shared" si="3"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="5">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5">
+        <v>66</v>
+      </c>
+      <c r="D10" s="7">
+        <v>36</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="1">
+        <f>SUM(C10:E10)</f>
+        <v>102</v>
+      </c>
+      <c r="G10" s="5">
+        <f>A2</f>
+        <v>30000</v>
+      </c>
+      <c r="H10" s="5">
+        <f>ROUNDUP(B10*G10/1000,0)</f>
+        <v>30</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="2"/>
+        <v>3.4</v>
+      </c>
+      <c r="J10" s="5">
+        <v>2</v>
+      </c>
+      <c r="K10" s="5">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="C11" s="5">
+        <v>25</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="1">
+        <f>SUM(C11:E11)</f>
+        <v>25</v>
+      </c>
+      <c r="G11" s="5">
+        <f>A2</f>
+        <v>30000</v>
+      </c>
+      <c r="H11" s="5">
+        <f>ROUNDUP(B11*G11/1000,0)</f>
+        <v>8</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="2"/>
+        <v>3.2</v>
+      </c>
+      <c r="J11" s="5">
+        <v>2</v>
+      </c>
+      <c r="K11" s="5">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="1">
+        <f>SUM(C12:E12)</f>
+        <v>2</v>
+      </c>
+      <c r="G12" s="5">
+        <f>A2</f>
+        <v>30000</v>
+      </c>
+      <c r="H12" s="5">
+        <f>ROUNDUP(B12*G12/1000,0)</f>
+        <v>8</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="2"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="J12" s="5">
+        <v>2</v>
+      </c>
+      <c r="K12" s="5">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/MainTop/ink statistic/ink statistic.xlsx
+++ b/MainTop/ink statistic/ink statistic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\ink statistic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6644C1B-EC90-4284-8E2F-5D8668F14B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D969BD-31F2-455B-9AC3-B26505C14ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,8 +20,9 @@
     <sheet name="Лист4" sheetId="5" r:id="rId5"/>
     <sheet name="Лист5" sheetId="6" r:id="rId6"/>
     <sheet name="остатки 12.05.2026" sheetId="8" r:id="rId7"/>
-    <sheet name="спрос" sheetId="9" r:id="rId8"/>
+    <sheet name="Лист8" sheetId="11" r:id="rId8"/>
     <sheet name="остатки" sheetId="10" r:id="rId9"/>
+    <sheet name="спрос" sheetId="12" r:id="rId10"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="47">
   <si>
     <t>k</t>
   </si>
@@ -89,21 +90,6 @@
     <t>в пути</t>
   </si>
   <si>
-    <t>punky monkey ВБ</t>
-  </si>
-  <si>
-    <t>amazing pics</t>
-  </si>
-  <si>
-    <t>amazing pics OZON</t>
-  </si>
-  <si>
-    <t>punky monkey OZON</t>
-  </si>
-  <si>
-    <t>punky monkey stickers OZON</t>
-  </si>
-  <si>
     <t>итого</t>
   </si>
   <si>
@@ -141,6 +127,54 @@
   </si>
   <si>
     <t>заказать на Х месяцев</t>
+  </si>
+  <si>
+    <t>1600 имен за 9,5 часов</t>
+  </si>
+  <si>
+    <t>спрос наклеек</t>
+  </si>
+  <si>
+    <t>Amazing Pics WB</t>
+  </si>
+  <si>
+    <t>Amazing Pics Ozon</t>
+  </si>
+  <si>
+    <t>Puunky Monkey Wb</t>
+  </si>
+  <si>
+    <t>Puunky Monkey Ozon</t>
+  </si>
+  <si>
+    <t>Puunky Monkey Stickers Ozon</t>
+  </si>
+  <si>
+    <t>в день</t>
+  </si>
+  <si>
+    <t>в месяц</t>
+  </si>
+  <si>
+    <t>цена</t>
+  </si>
+  <si>
+    <t>xiinflying</t>
+  </si>
+  <si>
+    <t>россия</t>
+  </si>
+  <si>
+    <t>06.06.2026 в пути</t>
+  </si>
+  <si>
+    <t>резка</t>
+  </si>
+  <si>
+    <t>упаковка</t>
+  </si>
+  <si>
+    <t>картон, кг</t>
   </si>
 </sst>
 </file>
@@ -165,7 +199,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -193,6 +227,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -224,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -251,6 +297,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -712,6 +764,89 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29078AD2-6CB5-4717-B063-37BABDC0A719}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.5703125" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B1" s="14">
+        <v>46179</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8">
+        <f>SUM(B3:B7)</f>
+        <v>784</v>
+      </c>
+      <c r="C8">
+        <f>B8*30</f>
+        <v>23520</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:B7"/>
@@ -1018,19 +1153,19 @@
         <v>17</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -1350,56 +1485,16 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{226A9FAA-9B28-4465-A0CA-F334D704BDBB}">
-  <dimension ref="A1:F2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D5DE18F-755D-409A-A2F2-6D186FECE930}">
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="21.140625" customWidth="1"/>
-    <col min="5" max="5" width="27.42578125" customWidth="1"/>
+    <col min="1" max="1" width="34.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2000</v>
-      </c>
-      <c r="B2">
-        <v>10400</v>
-      </c>
-      <c r="C2">
-        <v>3000</v>
-      </c>
-      <c r="D2">
-        <v>870</v>
-      </c>
-      <c r="E2">
-        <v>1400</v>
-      </c>
-      <c r="F2">
-        <f>SUM(A2:E2)</f>
-        <v>17670</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1409,19 +1504,23 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5752FFBB-2BA0-4D25-94B6-08B45A9708D1}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1"/>
     <col min="10" max="10" width="15.5703125" customWidth="1"/>
+    <col min="20" max="20" width="10.85546875" customWidth="1"/>
+    <col min="21" max="21" width="12.28515625" customWidth="1"/>
+    <col min="22" max="22" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1433,10 +1532,15 @@
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>30000</v>
+        <v>24000</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1448,10 +1552,15 @@
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
-    </row>
-    <row r="3" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+    </row>
+    <row r="3" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>16</v>
@@ -1465,25 +1574,34 @@
       <c r="E3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="5"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="F3" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" s="5"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="5">
@@ -1496,32 +1614,39 @@
         <v>7</v>
       </c>
       <c r="E4" s="6"/>
-      <c r="F4" s="1">
-        <f t="shared" ref="F4:F8" si="0">SUM(C4:E4)</f>
-        <v>11</v>
-      </c>
-      <c r="G4" s="5">
+      <c r="F4" s="6">
+        <v>6</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="1">
+        <f>SUM(C4:G4)</f>
+        <v>17</v>
+      </c>
+      <c r="I4" s="5">
         <f>A2</f>
-        <v>30000</v>
-      </c>
-      <c r="H4" s="5">
-        <f t="shared" ref="H4:H9" si="1">ROUNDUP(B4*G4/1000,0)</f>
+        <v>24000</v>
+      </c>
+      <c r="J4" s="5">
+        <f>ROUNDUP(B4*I4/1000,0)</f>
         <v>3</v>
       </c>
-      <c r="I4" s="5">
-        <f>ROUNDUP(F4/H4,1)</f>
-        <v>3.7</v>
-      </c>
-      <c r="J4" s="5">
+      <c r="K4" s="5">
+        <f>ROUNDUP(H4/J4,1)</f>
+        <v>5.6999999999999993</v>
+      </c>
+      <c r="L4" s="5">
         <v>2</v>
       </c>
-      <c r="K4" s="5">
-        <f>H4*J4</f>
+      <c r="M4" s="5">
+        <f>J4*L4</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="5">
@@ -1534,32 +1659,39 @@
         <v>7</v>
       </c>
       <c r="E5" s="6"/>
-      <c r="F5" s="1">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="G5" s="5">
+      <c r="F5" s="6">
+        <v>6</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="1">
+        <f t="shared" ref="H5:H17" si="0">SUM(C5:G5)</f>
+        <v>17</v>
+      </c>
+      <c r="I5" s="5">
         <f>A2</f>
-        <v>30000</v>
-      </c>
-      <c r="H5" s="5">
-        <f t="shared" si="1"/>
+        <v>24000</v>
+      </c>
+      <c r="J5" s="5">
+        <f>ROUNDUP(B5*I5/1000,0)</f>
         <v>3</v>
       </c>
-      <c r="I5" s="5">
-        <f t="shared" ref="I5:I12" si="2">ROUNDUP(F5/H5,1)</f>
-        <v>3.7</v>
-      </c>
-      <c r="J5" s="5">
+      <c r="K5" s="5">
+        <f>ROUNDUP(H5/J5,1)</f>
+        <v>5.6999999999999993</v>
+      </c>
+      <c r="L5" s="5">
         <v>2</v>
       </c>
-      <c r="K5" s="5">
-        <f t="shared" ref="K5:K12" si="3">H5*J5</f>
+      <c r="M5" s="5">
+        <f t="shared" ref="M5:M12" si="1">J5*L5</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="5">
@@ -1572,32 +1704,39 @@
         <v>15</v>
       </c>
       <c r="E6" s="6"/>
-      <c r="F6" s="1">
+      <c r="F6" s="6">
+        <v>10</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="1">
         <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="G6" s="5">
+        <v>31</v>
+      </c>
+      <c r="I6" s="5">
         <f>A2</f>
-        <v>30000</v>
-      </c>
-      <c r="H6" s="5">
+        <v>24000</v>
+      </c>
+      <c r="J6" s="5">
+        <f>ROUNDUP(B6*I6/1000,0)</f>
+        <v>5</v>
+      </c>
+      <c r="K6" s="5">
+        <f>ROUNDUP(H6/J6,1)</f>
+        <v>6.2</v>
+      </c>
+      <c r="L6" s="5">
+        <v>2</v>
+      </c>
+      <c r="M6" s="5">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="2"/>
-        <v>3.5</v>
-      </c>
-      <c r="J6" s="5">
-        <v>2</v>
-      </c>
-      <c r="K6" s="5">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="5">
@@ -1610,36 +1749,52 @@
         <v>21</v>
       </c>
       <c r="E7" s="6"/>
-      <c r="F7" s="1">
+      <c r="F7" s="6">
+        <v>12</v>
+      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="1">
         <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="G7" s="5">
+        <v>42</v>
+      </c>
+      <c r="I7" s="5">
         <f>A2</f>
-        <v>30000</v>
-      </c>
-      <c r="H7" s="5">
+        <v>24000</v>
+      </c>
+      <c r="J7" s="5">
+        <f>ROUNDUP(B7*I7/1000,0)</f>
+        <v>6</v>
+      </c>
+      <c r="K7" s="5">
+        <f>ROUNDUP(H7/J7,1)</f>
+        <v>7</v>
+      </c>
+      <c r="L7" s="5">
+        <v>2</v>
+      </c>
+      <c r="M7" s="5">
         <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="2"/>
-        <v>3.8000000000000003</v>
-      </c>
-      <c r="J7" s="5">
-        <v>2</v>
-      </c>
-      <c r="K7" s="5">
-        <f t="shared" si="3"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="T7">
+        <v>1688</v>
+      </c>
+      <c r="U7" t="s">
+        <v>41</v>
+      </c>
+      <c r="V7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="5">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="C8" s="5">
         <v>130</v>
@@ -1648,32 +1803,52 @@
         <v>130</v>
       </c>
       <c r="E8" s="6"/>
-      <c r="F8" s="1">
+      <c r="F8" s="6">
+        <v>126</v>
+      </c>
+      <c r="G8" s="5"/>
+      <c r="H8" s="1">
         <f t="shared" si="0"/>
-        <v>260</v>
-      </c>
-      <c r="G8" s="5">
+        <v>386</v>
+      </c>
+      <c r="I8" s="5">
         <f>A2</f>
-        <v>30000</v>
-      </c>
-      <c r="H8" s="5">
+        <v>24000</v>
+      </c>
+      <c r="J8" s="5">
+        <f>ROUNDUP(B8*I8/1000,0)</f>
+        <v>63</v>
+      </c>
+      <c r="K8" s="5">
+        <f>ROUNDUP(H8/J8,1)</f>
+        <v>6.1999999999999993</v>
+      </c>
+      <c r="L8" s="5">
+        <v>2</v>
+      </c>
+      <c r="M8" s="5">
         <f t="shared" si="1"/>
-        <v>75</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="2"/>
-        <v>3.5</v>
-      </c>
-      <c r="J8" s="5">
-        <v>2</v>
-      </c>
-      <c r="K8" s="5">
-        <f t="shared" si="3"/>
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="N8" s="5">
+        <f>SUM(M4:M8)</f>
+        <v>160</v>
+      </c>
+      <c r="O8" s="5">
+        <f>N8*22+N8*3.2*90+950*90</f>
+        <v>135100</v>
+      </c>
+      <c r="P8" s="5">
+        <f>O8*2</f>
+        <v>270200</v>
+      </c>
+      <c r="R8">
+        <f>950+M9*5</f>
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="5">
@@ -1688,32 +1863,53 @@
       <c r="E9" s="8">
         <v>260</v>
       </c>
-      <c r="F9" s="1">
-        <f>SUM(C9:E9)</f>
+      <c r="G9" s="5"/>
+      <c r="H9" s="1">
+        <f t="shared" si="0"/>
         <v>480</v>
       </c>
-      <c r="G9" s="5">
+      <c r="I9" s="5">
         <f>A2</f>
-        <v>30000</v>
-      </c>
-      <c r="H9" s="5">
+        <v>24000</v>
+      </c>
+      <c r="J9" s="5">
+        <f>ROUNDUP(B9*I9/1000,0)</f>
+        <v>96</v>
+      </c>
+      <c r="K9" s="5">
+        <f>ROUNDUP(H9/J9,1)</f>
+        <v>5</v>
+      </c>
+      <c r="L9" s="5">
+        <v>2</v>
+      </c>
+      <c r="M9" s="5">
         <f t="shared" si="1"/>
-        <v>120</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="J9" s="5">
-        <v>2</v>
-      </c>
-      <c r="K9" s="5">
-        <f t="shared" si="3"/>
-        <v>240</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5">
+        <f>M9*3.2*90+M9*22</f>
+        <v>59520.000000000007</v>
+      </c>
+      <c r="P9" s="5">
+        <f>O9*2</f>
+        <v>119040.00000000001</v>
+      </c>
+      <c r="T9">
+        <f>(3.48+3.2)*90+22</f>
+        <v>623.19999999999993</v>
+      </c>
+      <c r="U9">
+        <f>8.2*90+1*22</f>
+        <v>759.99999999999989</v>
+      </c>
+      <c r="V9">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="5">
@@ -1726,32 +1922,57 @@
         <v>36</v>
       </c>
       <c r="E10" s="6"/>
-      <c r="F10" s="1">
-        <f>SUM(C10:E10)</f>
+      <c r="G10" s="5"/>
+      <c r="H10" s="1">
+        <f t="shared" si="0"/>
         <v>102</v>
       </c>
-      <c r="G10" s="5">
+      <c r="I10" s="5">
         <f>A2</f>
-        <v>30000</v>
-      </c>
-      <c r="H10" s="5">
-        <f>ROUNDUP(B10*G10/1000,0)</f>
-        <v>30</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="2"/>
-        <v>3.4</v>
+        <v>24000</v>
       </c>
       <c r="J10" s="5">
+        <f>ROUNDUP(B10*I10/1000,0)</f>
+        <v>24</v>
+      </c>
+      <c r="K10" s="5">
+        <f>ROUNDUP(H10/J10,1)</f>
+        <v>4.3</v>
+      </c>
+      <c r="L10" s="5">
         <v>2</v>
       </c>
-      <c r="K10" s="5">
-        <f t="shared" si="3"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="M10" s="5">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5">
+        <f>M10*3800+M10*22</f>
+        <v>183456</v>
+      </c>
+      <c r="P10" s="5">
+        <f>100*3600+100*22</f>
+        <v>362200</v>
+      </c>
+      <c r="S10" s="5">
+        <v>192</v>
+      </c>
+      <c r="T10">
+        <f>T9*S10</f>
+        <v>119654.39999999999</v>
+      </c>
+      <c r="U10">
+        <f>U9*S10</f>
+        <v>145919.99999999997</v>
+      </c>
+      <c r="V10">
+        <f>V9*S10</f>
+        <v>178560</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="5">
@@ -1762,31 +1983,41 @@
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="6"/>
-      <c r="F11" s="1">
-        <f>SUM(C11:E11)</f>
+      <c r="G11" s="5"/>
+      <c r="H11" s="1">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="G11" s="5">
+      <c r="I11" s="5">
         <f>A2</f>
-        <v>30000</v>
-      </c>
-      <c r="H11" s="5">
-        <f>ROUNDUP(B11*G11/1000,0)</f>
-        <v>8</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" si="2"/>
-        <v>3.2</v>
+        <v>24000</v>
       </c>
       <c r="J11" s="5">
+        <f>ROUNDUP(B11*I11/1000,0)</f>
+        <v>6</v>
+      </c>
+      <c r="K11" s="5">
+        <f>ROUNDUP(H11/J11,1)</f>
+        <v>4.1999999999999993</v>
+      </c>
+      <c r="L11" s="5">
         <v>2</v>
       </c>
-      <c r="K11" s="5">
-        <f t="shared" si="3"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M11" s="5">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="N11" s="5"/>
+      <c r="O11" s="19">
+        <f>SUM(O8:O10)</f>
+        <v>378076</v>
+      </c>
+      <c r="P11" s="19">
+        <f>SUM(P8:P10)</f>
+        <v>751440</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>13</v>
       </c>
@@ -1798,33 +2029,37 @@
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="6"/>
-      <c r="F12" s="1">
-        <f>SUM(C12:E12)</f>
+      <c r="G12" s="5"/>
+      <c r="H12" s="1">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G12" s="5">
+      <c r="I12" s="5">
         <f>A2</f>
-        <v>30000</v>
-      </c>
-      <c r="H12" s="5">
-        <f>ROUNDUP(B12*G12/1000,0)</f>
-        <v>8</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="2"/>
-        <v>0.30000000000000004</v>
+        <v>24000</v>
       </c>
       <c r="J12" s="5">
+        <f>ROUNDUP(B12*I12/1000,0)</f>
+        <v>6</v>
+      </c>
+      <c r="K12" s="5">
+        <f>ROUNDUP(H12/J12,1)</f>
+        <v>0.4</v>
+      </c>
+      <c r="L12" s="5">
         <v>2</v>
       </c>
-      <c r="K12" s="5">
-        <f t="shared" si="3"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M12" s="5">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -1832,14 +2067,25 @@
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
+      <c r="H13" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
+      <c r="J13" s="5">
+        <f t="shared" ref="J13:J17" si="2">ROUNDUP(B13*I13/1000,0)</f>
+        <v>0</v>
+      </c>
       <c r="K13" s="5"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -1847,14 +2093,25 @@
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
+      <c r="H14" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
+      <c r="J14" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K14" s="5"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -1862,40 +2119,142 @@
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
+      <c r="H15" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
+      <c r="J15" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="K15" s="5"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
+        <v>25</v>
+      </c>
+      <c r="B16" s="5">
+        <f>A2*0.75/24</f>
+        <v>750</v>
+      </c>
+      <c r="C16" s="5">
+        <v>25000</v>
+      </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H16" s="1">
+        <f t="shared" si="0"/>
+        <v>25000</v>
+      </c>
+      <c r="I16" s="5">
+        <f>A2</f>
+        <v>24000</v>
+      </c>
+      <c r="J16" s="5">
+        <f t="shared" si="2"/>
+        <v>18000</v>
+      </c>
+      <c r="K16" s="5">
+        <f t="shared" ref="K16:K17" si="3">ROUNDUP(H16/J16,1)</f>
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="B17" s="5">
+        <f>A2*0.25/24</f>
+        <v>250</v>
+      </c>
+      <c r="C17" s="5">
+        <v>50000</v>
+      </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
+      <c r="H17" s="1">
+        <f t="shared" si="0"/>
+        <v>50000</v>
+      </c>
+      <c r="I17" s="5">
+        <f>A2</f>
+        <v>24000</v>
+      </c>
+      <c r="J17" s="5">
+        <f t="shared" si="2"/>
+        <v>6000</v>
+      </c>
+      <c r="K17" s="5">
+        <f t="shared" si="3"/>
+        <v>8.4</v>
+      </c>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18">
+        <v>17.850000000000001</v>
+      </c>
+      <c r="C18">
+        <v>610</v>
+      </c>
+      <c r="D18">
+        <v>240</v>
+      </c>
+      <c r="H18" s="1">
+        <f t="shared" ref="H18" si="4">SUM(C18:G18)</f>
+        <v>850</v>
+      </c>
+      <c r="I18" s="5">
+        <f>A2</f>
+        <v>24000</v>
+      </c>
+      <c r="J18" s="5">
+        <f>ROUNDUP(B18*I18/1000,0)</f>
+        <v>429</v>
+      </c>
+      <c r="K18" s="5">
+        <f>ROUNDUP(H18/J18,1)</f>
+        <v>2</v>
+      </c>
+      <c r="L18" s="5">
+        <v>2</v>
+      </c>
+      <c r="M18" s="5">
+        <f>J18*L18</f>
+        <v>858</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MainTop/ink statistic/ink statistic.xlsx
+++ b/MainTop/ink statistic/ink statistic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\ink statistic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D969BD-31F2-455B-9AC3-B26505C14ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD015CD-F4D7-4ECE-8395-73E3B5529239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/MainTop/ink statistic/ink statistic.xlsx
+++ b/MainTop/ink statistic/ink statistic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\ink statistic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD015CD-F4D7-4ECE-8395-73E3B5529239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98EAB0B7-46C2-4E52-8923-3DCEFAF80265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1627,11 +1627,11 @@
         <v>24000</v>
       </c>
       <c r="J4" s="5">
-        <f>ROUNDUP(B4*I4/1000,0)</f>
+        <f t="shared" ref="J4:J12" si="0">ROUNDUP(B4*I4/1000,0)</f>
         <v>3</v>
       </c>
       <c r="K4" s="5">
-        <f>ROUNDUP(H4/J4,1)</f>
+        <f t="shared" ref="K4:K12" si="1">ROUNDUP(H4/J4,1)</f>
         <v>5.6999999999999993</v>
       </c>
       <c r="L4" s="5">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="1">
-        <f t="shared" ref="H5:H17" si="0">SUM(C5:G5)</f>
+        <f t="shared" ref="H5:H17" si="2">SUM(C5:G5)</f>
         <v>17</v>
       </c>
       <c r="I5" s="5">
@@ -1672,18 +1672,18 @@
         <v>24000</v>
       </c>
       <c r="J5" s="5">
-        <f>ROUNDUP(B5*I5/1000,0)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="K5" s="5">
-        <f>ROUNDUP(H5/J5,1)</f>
+        <f t="shared" si="1"/>
         <v>5.6999999999999993</v>
       </c>
       <c r="L5" s="5">
         <v>2</v>
       </c>
       <c r="M5" s="5">
-        <f t="shared" ref="M5:M12" si="1">J5*L5</f>
+        <f t="shared" ref="M5:M12" si="3">J5*L5</f>
         <v>6</v>
       </c>
       <c r="N5" s="5"/>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="I6" s="5">
@@ -1717,18 +1717,18 @@
         <v>24000</v>
       </c>
       <c r="J6" s="5">
-        <f>ROUNDUP(B6*I6/1000,0)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="K6" s="5">
-        <f>ROUNDUP(H6/J6,1)</f>
+        <f t="shared" si="1"/>
         <v>6.2</v>
       </c>
       <c r="L6" s="5">
         <v>2</v>
       </c>
       <c r="M6" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="N6" s="5"/>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>42</v>
       </c>
       <c r="I7" s="5">
@@ -1762,18 +1762,18 @@
         <v>24000</v>
       </c>
       <c r="J7" s="5">
-        <f>ROUNDUP(B7*I7/1000,0)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="K7" s="5">
-        <f>ROUNDUP(H7/J7,1)</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="L7" s="5">
         <v>2</v>
       </c>
       <c r="M7" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="N7" s="5"/>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>386</v>
       </c>
       <c r="I8" s="5">
@@ -1816,18 +1816,18 @@
         <v>24000</v>
       </c>
       <c r="J8" s="5">
-        <f>ROUNDUP(B8*I8/1000,0)</f>
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="K8" s="5">
-        <f>ROUNDUP(H8/J8,1)</f>
+        <f t="shared" si="1"/>
         <v>6.1999999999999993</v>
       </c>
       <c r="L8" s="5">
         <v>2</v>
       </c>
       <c r="M8" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>126</v>
       </c>
       <c r="N8" s="5">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>480</v>
       </c>
       <c r="I9" s="5">
@@ -1873,18 +1873,18 @@
         <v>24000</v>
       </c>
       <c r="J9" s="5">
-        <f>ROUNDUP(B9*I9/1000,0)</f>
+        <f t="shared" si="0"/>
         <v>96</v>
       </c>
       <c r="K9" s="5">
-        <f>ROUNDUP(H9/J9,1)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="L9" s="5">
         <v>2</v>
       </c>
       <c r="M9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>192</v>
       </c>
       <c r="N9" s="5"/>
@@ -1924,7 +1924,7 @@
       <c r="E10" s="6"/>
       <c r="G10" s="5"/>
       <c r="H10" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>102</v>
       </c>
       <c r="I10" s="5">
@@ -1932,18 +1932,18 @@
         <v>24000</v>
       </c>
       <c r="J10" s="5">
-        <f>ROUNDUP(B10*I10/1000,0)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="K10" s="5">
-        <f>ROUNDUP(H10/J10,1)</f>
+        <f t="shared" si="1"/>
         <v>4.3</v>
       </c>
       <c r="L10" s="5">
         <v>2</v>
       </c>
       <c r="M10" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>48</v>
       </c>
       <c r="N10" s="5"/>
@@ -1985,7 +1985,7 @@
       <c r="E11" s="6"/>
       <c r="G11" s="5"/>
       <c r="H11" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="I11" s="5">
@@ -1993,18 +1993,18 @@
         <v>24000</v>
       </c>
       <c r="J11" s="5">
-        <f>ROUNDUP(B11*I11/1000,0)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="K11" s="5">
-        <f>ROUNDUP(H11/J11,1)</f>
+        <f t="shared" si="1"/>
         <v>4.1999999999999993</v>
       </c>
       <c r="L11" s="5">
         <v>2</v>
       </c>
       <c r="M11" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="N11" s="5"/>
@@ -2031,7 +2031,7 @@
       <c r="E12" s="6"/>
       <c r="G12" s="5"/>
       <c r="H12" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="I12" s="5">
@@ -2039,18 +2039,18 @@
         <v>24000</v>
       </c>
       <c r="J12" s="5">
-        <f>ROUNDUP(B12*I12/1000,0)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="K12" s="5">
-        <f>ROUNDUP(H12/J12,1)</f>
+        <f t="shared" si="1"/>
         <v>0.4</v>
       </c>
       <c r="L12" s="5">
         <v>2</v>
       </c>
       <c r="M12" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="N12" s="5"/>
@@ -2068,12 +2068,12 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5">
-        <f t="shared" ref="J13:J17" si="2">ROUNDUP(B13*I13/1000,0)</f>
+        <f t="shared" ref="J13:J17" si="4">ROUNDUP(B13*I13/1000,0)</f>
         <v>0</v>
       </c>
       <c r="K13" s="5"/>
@@ -2094,12 +2094,12 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K14" s="5"/>
@@ -2120,12 +2120,12 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K15" s="5"/>
@@ -2151,7 +2151,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>25000</v>
       </c>
       <c r="I16" s="5">
@@ -2159,11 +2159,11 @@
         <v>24000</v>
       </c>
       <c r="J16" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>18000</v>
       </c>
       <c r="K16" s="5">
-        <f t="shared" ref="K16:K17" si="3">ROUNDUP(H16/J16,1)</f>
+        <f t="shared" ref="K16:K17" si="5">ROUNDUP(H16/J16,1)</f>
         <v>1.4000000000000001</v>
       </c>
       <c r="L16" s="5"/>
@@ -2188,7 +2188,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>50000</v>
       </c>
       <c r="I17" s="5">
@@ -2196,11 +2196,11 @@
         <v>24000</v>
       </c>
       <c r="J17" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6000</v>
       </c>
       <c r="K17" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>8.4</v>
       </c>
       <c r="L17" s="5"/>
@@ -2223,7 +2223,7 @@
         <v>240</v>
       </c>
       <c r="H18" s="1">
-        <f t="shared" ref="H18" si="4">SUM(C18:G18)</f>
+        <f t="shared" ref="H18" si="6">SUM(C18:G18)</f>
         <v>850</v>
       </c>
       <c r="I18" s="5">

--- a/MainTop/ink statistic/ink statistic.xlsx
+++ b/MainTop/ink statistic/ink statistic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\ink statistic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98EAB0B7-46C2-4E52-8923-3DCEFAF80265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40973311-F34F-4A52-A7FF-FD95BD956FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="48">
   <si>
     <t>k</t>
   </si>
@@ -175,6 +175,9 @@
   </si>
   <si>
     <t>картон, кг</t>
+  </si>
+  <si>
+    <t>заказать</t>
   </si>
 </sst>
 </file>
@@ -243,7 +246,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -266,11 +269,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -303,6 +317,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1577,7 +1592,9 @@
       <c r="F3" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G3" s="5"/>
+      <c r="G3" s="11" t="s">
+        <v>47</v>
+      </c>
       <c r="H3" s="12" t="s">
         <v>21</v>
       </c>
@@ -1608,19 +1625,20 @@
         <v>0.09</v>
       </c>
       <c r="C4" s="5">
-        <v>4</v>
-      </c>
-      <c r="D4" s="7">
+        <v>2</v>
+      </c>
+      <c r="E4" s="7">
         <v>7</v>
       </c>
-      <c r="E4" s="6"/>
       <c r="F4" s="6">
         <v>6</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4" s="6">
+        <v>8</v>
+      </c>
       <c r="H4" s="1">
         <f>SUM(C4:G4)</f>
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I4" s="5">
         <f>A2</f>
@@ -1632,7 +1650,7 @@
       </c>
       <c r="K4" s="5">
         <f t="shared" ref="K4:K12" si="1">ROUNDUP(H4/J4,1)</f>
-        <v>5.6999999999999993</v>
+        <v>7.6999999999999993</v>
       </c>
       <c r="L4" s="5">
         <v>2</v>
@@ -1653,19 +1671,20 @@
         <v>0.09</v>
       </c>
       <c r="C5" s="5">
-        <v>4</v>
-      </c>
-      <c r="D5" s="7">
+        <v>3</v>
+      </c>
+      <c r="E5" s="7">
         <v>7</v>
       </c>
-      <c r="E5" s="6"/>
       <c r="F5" s="6">
         <v>6</v>
       </c>
-      <c r="G5" s="5"/>
+      <c r="G5" s="6">
+        <v>8</v>
+      </c>
       <c r="H5" s="1">
-        <f t="shared" ref="H5:H17" si="2">SUM(C5:G5)</f>
-        <v>17</v>
+        <f>SUM(C5:G5)</f>
+        <v>24</v>
       </c>
       <c r="I5" s="5">
         <f>A2</f>
@@ -1677,13 +1696,13 @@
       </c>
       <c r="K5" s="5">
         <f t="shared" si="1"/>
-        <v>5.6999999999999993</v>
+        <v>8</v>
       </c>
       <c r="L5" s="5">
         <v>2</v>
       </c>
       <c r="M5" s="5">
-        <f t="shared" ref="M5:M12" si="3">J5*L5</f>
+        <f t="shared" ref="M5:M12" si="2">J5*L5</f>
         <v>6</v>
       </c>
       <c r="N5" s="5"/>
@@ -1698,19 +1717,20 @@
         <v>0.19</v>
       </c>
       <c r="C6" s="5">
-        <v>6</v>
-      </c>
-      <c r="D6" s="7">
+        <v>4</v>
+      </c>
+      <c r="E6" s="7">
         <v>15</v>
       </c>
-      <c r="E6" s="6"/>
       <c r="F6" s="6">
         <v>10</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6" s="6">
+        <v>10</v>
+      </c>
       <c r="H6" s="1">
-        <f t="shared" si="2"/>
-        <v>31</v>
+        <f>SUM(C6:G6)</f>
+        <v>39</v>
       </c>
       <c r="I6" s="5">
         <f>A2</f>
@@ -1722,13 +1742,13 @@
       </c>
       <c r="K6" s="5">
         <f t="shared" si="1"/>
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="L6" s="5">
         <v>2</v>
       </c>
       <c r="M6" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N6" s="5"/>
@@ -1743,19 +1763,20 @@
         <v>0.24</v>
       </c>
       <c r="C7" s="5">
-        <v>9</v>
-      </c>
-      <c r="D7" s="7">
+        <v>7</v>
+      </c>
+      <c r="E7" s="7">
         <v>21</v>
       </c>
-      <c r="E7" s="6"/>
       <c r="F7" s="6">
         <v>12</v>
       </c>
-      <c r="G7" s="5"/>
+      <c r="G7" s="6">
+        <v>8</v>
+      </c>
       <c r="H7" s="1">
-        <f t="shared" si="2"/>
-        <v>42</v>
+        <f>SUM(C7:G7)</f>
+        <v>48</v>
       </c>
       <c r="I7" s="5">
         <f>A2</f>
@@ -1767,13 +1788,13 @@
       </c>
       <c r="K7" s="5">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L7" s="5">
         <v>2</v>
       </c>
       <c r="M7" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="N7" s="5"/>
@@ -1797,19 +1818,20 @@
         <v>2.6</v>
       </c>
       <c r="C8" s="5">
+        <v>103</v>
+      </c>
+      <c r="E8" s="7">
         <v>130</v>
       </c>
-      <c r="D8" s="7">
-        <v>130</v>
-      </c>
-      <c r="E8" s="6"/>
       <c r="F8" s="6">
         <v>126</v>
       </c>
-      <c r="G8" s="5"/>
+      <c r="G8" s="6">
+        <v>126</v>
+      </c>
       <c r="H8" s="1">
-        <f t="shared" si="2"/>
-        <v>386</v>
+        <f>SUM(C8:G8)</f>
+        <v>485</v>
       </c>
       <c r="I8" s="5">
         <f>A2</f>
@@ -1821,13 +1843,13 @@
       </c>
       <c r="K8" s="5">
         <f t="shared" si="1"/>
-        <v>6.1999999999999993</v>
+        <v>7.6999999999999993</v>
       </c>
       <c r="L8" s="5">
         <v>2</v>
       </c>
       <c r="M8" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>126</v>
       </c>
       <c r="N8" s="5">
@@ -1855,18 +1877,21 @@
         <v>4</v>
       </c>
       <c r="C9" s="5">
-        <v>100</v>
-      </c>
-      <c r="D9" s="8">
-        <v>120</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="D9" s="8"/>
       <c r="E9" s="8">
         <v>260</v>
       </c>
-      <c r="G9" s="5"/>
+      <c r="F9" s="20">
+        <v>190</v>
+      </c>
+      <c r="G9" s="20">
+        <v>190</v>
+      </c>
       <c r="H9" s="1">
-        <f t="shared" si="2"/>
-        <v>480</v>
+        <f>SUM(C9:G9)</f>
+        <v>780</v>
       </c>
       <c r="I9" s="5">
         <f>A2</f>
@@ -1878,13 +1903,13 @@
       </c>
       <c r="K9" s="5">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="L9" s="5">
         <v>2</v>
       </c>
       <c r="M9" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>192</v>
       </c>
       <c r="N9" s="5"/>
@@ -1916,16 +1941,16 @@
         <v>1</v>
       </c>
       <c r="C10" s="5">
-        <v>66</v>
-      </c>
-      <c r="D10" s="7">
-        <v>36</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="D10" s="7"/>
       <c r="E10" s="6"/>
-      <c r="G10" s="5"/>
+      <c r="G10" s="6">
+        <v>100</v>
+      </c>
       <c r="H10" s="1">
-        <f t="shared" si="2"/>
-        <v>102</v>
+        <f t="shared" ref="H10:H17" si="3">SUM(C10:G10)</f>
+        <v>188</v>
       </c>
       <c r="I10" s="5">
         <f>A2</f>
@@ -1937,13 +1962,13 @@
       </c>
       <c r="K10" s="5">
         <f t="shared" si="1"/>
-        <v>4.3</v>
+        <v>7.8999999999999995</v>
       </c>
       <c r="L10" s="5">
         <v>2</v>
       </c>
       <c r="M10" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>48</v>
       </c>
       <c r="N10" s="5"/>
@@ -1985,7 +2010,7 @@
       <c r="E11" s="6"/>
       <c r="G11" s="5"/>
       <c r="H11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="I11" s="5">
@@ -2004,7 +2029,7 @@
         <v>2</v>
       </c>
       <c r="M11" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="N11" s="5"/>
@@ -2031,7 +2056,7 @@
       <c r="E12" s="6"/>
       <c r="G12" s="5"/>
       <c r="H12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="I12" s="5">
@@ -2050,7 +2075,7 @@
         <v>2</v>
       </c>
       <c r="M12" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="N12" s="5"/>
@@ -2068,7 +2093,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I13" s="5"/>
@@ -2094,7 +2119,7 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I14" s="5"/>
@@ -2120,7 +2145,7 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I15" s="5"/>
@@ -2151,7 +2176,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>25000</v>
       </c>
       <c r="I16" s="5">
@@ -2188,7 +2213,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>50000</v>
       </c>
       <c r="I17" s="5">

--- a/MainTop/ink statistic/ink statistic.xlsx
+++ b/MainTop/ink statistic/ink statistic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\ink statistic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40973311-F34F-4A52-A7FF-FD95BD956FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAA05967-68BD-4F84-B591-7337CC082DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -177,7 +177,7 @@
     <t>картон, кг</t>
   </si>
   <si>
-    <t>заказать</t>
+    <t>22.06.2026 в пути</t>
   </si>
 </sst>
 </file>
@@ -1637,7 +1637,7 @@
         <v>8</v>
       </c>
       <c r="H4" s="1">
-        <f>SUM(C4:G4)</f>
+        <f t="shared" ref="H4:H9" si="0">SUM(C4:G4)</f>
         <v>23</v>
       </c>
       <c r="I4" s="5">
@@ -1645,11 +1645,11 @@
         <v>24000</v>
       </c>
       <c r="J4" s="5">
-        <f t="shared" ref="J4:J12" si="0">ROUNDUP(B4*I4/1000,0)</f>
+        <f t="shared" ref="J4:J12" si="1">ROUNDUP(B4*I4/1000,0)</f>
         <v>3</v>
       </c>
       <c r="K4" s="5">
-        <f t="shared" ref="K4:K12" si="1">ROUNDUP(H4/J4,1)</f>
+        <f t="shared" ref="K4:K12" si="2">ROUNDUP(H4/J4,1)</f>
         <v>7.6999999999999993</v>
       </c>
       <c r="L4" s="5">
@@ -1683,7 +1683,7 @@
         <v>8</v>
       </c>
       <c r="H5" s="1">
-        <f>SUM(C5:G5)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="I5" s="5">
@@ -1691,18 +1691,18 @@
         <v>24000</v>
       </c>
       <c r="J5" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="K5" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="L5" s="5">
         <v>2</v>
       </c>
       <c r="M5" s="5">
-        <f t="shared" ref="M5:M12" si="2">J5*L5</f>
+        <f t="shared" ref="M5:M12" si="3">J5*L5</f>
         <v>6</v>
       </c>
       <c r="N5" s="5"/>
@@ -1729,7 +1729,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="1">
-        <f>SUM(C6:G6)</f>
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="I6" s="5">
@@ -1737,18 +1737,18 @@
         <v>24000</v>
       </c>
       <c r="J6" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="K6" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.8</v>
       </c>
       <c r="L6" s="5">
         <v>2</v>
       </c>
       <c r="M6" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="N6" s="5"/>
@@ -1775,7 +1775,7 @@
         <v>8</v>
       </c>
       <c r="H7" s="1">
-        <f>SUM(C7:G7)</f>
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="I7" s="5">
@@ -1783,18 +1783,18 @@
         <v>24000</v>
       </c>
       <c r="J7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="K7" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="L7" s="5">
         <v>2</v>
       </c>
       <c r="M7" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="N7" s="5"/>
@@ -1830,7 +1830,7 @@
         <v>126</v>
       </c>
       <c r="H8" s="1">
-        <f>SUM(C8:G8)</f>
+        <f t="shared" si="0"/>
         <v>485</v>
       </c>
       <c r="I8" s="5">
@@ -1838,18 +1838,18 @@
         <v>24000</v>
       </c>
       <c r="J8" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>63</v>
       </c>
       <c r="K8" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.6999999999999993</v>
       </c>
       <c r="L8" s="5">
         <v>2</v>
       </c>
       <c r="M8" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>126</v>
       </c>
       <c r="N8" s="5">
@@ -1890,7 +1890,7 @@
         <v>190</v>
       </c>
       <c r="H9" s="1">
-        <f>SUM(C9:G9)</f>
+        <f t="shared" si="0"/>
         <v>780</v>
       </c>
       <c r="I9" s="5">
@@ -1898,18 +1898,18 @@
         <v>24000</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>96</v>
       </c>
       <c r="K9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.1999999999999993</v>
       </c>
       <c r="L9" s="5">
         <v>2</v>
       </c>
       <c r="M9" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>192</v>
       </c>
       <c r="N9" s="5"/>
@@ -1949,7 +1949,7 @@
         <v>100</v>
       </c>
       <c r="H10" s="1">
-        <f t="shared" ref="H10:H17" si="3">SUM(C10:G10)</f>
+        <f t="shared" ref="H10:H17" si="4">SUM(C10:G10)</f>
         <v>188</v>
       </c>
       <c r="I10" s="5">
@@ -1957,18 +1957,18 @@
         <v>24000</v>
       </c>
       <c r="J10" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="K10" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.8999999999999995</v>
       </c>
       <c r="L10" s="5">
         <v>2</v>
       </c>
       <c r="M10" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>48</v>
       </c>
       <c r="N10" s="5"/>
@@ -2010,7 +2010,7 @@
       <c r="E11" s="6"/>
       <c r="G11" s="5"/>
       <c r="H11" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="I11" s="5">
@@ -2018,18 +2018,18 @@
         <v>24000</v>
       </c>
       <c r="J11" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="K11" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.1999999999999993</v>
       </c>
       <c r="L11" s="5">
         <v>2</v>
       </c>
       <c r="M11" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="N11" s="5"/>
@@ -2056,7 +2056,7 @@
       <c r="E12" s="6"/>
       <c r="G12" s="5"/>
       <c r="H12" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="I12" s="5">
@@ -2064,18 +2064,18 @@
         <v>24000</v>
       </c>
       <c r="J12" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="K12" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
       <c r="L12" s="5">
         <v>2</v>
       </c>
       <c r="M12" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="N12" s="5"/>
@@ -2093,12 +2093,12 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5">
-        <f t="shared" ref="J13:J17" si="4">ROUNDUP(B13*I13/1000,0)</f>
+        <f t="shared" ref="J13:J17" si="5">ROUNDUP(B13*I13/1000,0)</f>
         <v>0</v>
       </c>
       <c r="K13" s="5"/>
@@ -2119,12 +2119,12 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K14" s="5"/>
@@ -2145,12 +2145,12 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K15" s="5"/>
@@ -2176,7 +2176,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>25000</v>
       </c>
       <c r="I16" s="5">
@@ -2184,11 +2184,11 @@
         <v>24000</v>
       </c>
       <c r="J16" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>18000</v>
       </c>
       <c r="K16" s="5">
-        <f t="shared" ref="K16:K17" si="5">ROUNDUP(H16/J16,1)</f>
+        <f t="shared" ref="K16:K17" si="6">ROUNDUP(H16/J16,1)</f>
         <v>1.4000000000000001</v>
       </c>
       <c r="L16" s="5"/>
@@ -2213,7 +2213,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>50000</v>
       </c>
       <c r="I17" s="5">
@@ -2221,11 +2221,11 @@
         <v>24000</v>
       </c>
       <c r="J17" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6000</v>
       </c>
       <c r="K17" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.4</v>
       </c>
       <c r="L17" s="5"/>
@@ -2248,7 +2248,7 @@
         <v>240</v>
       </c>
       <c r="H18" s="1">
-        <f t="shared" ref="H18" si="6">SUM(C18:G18)</f>
+        <f t="shared" ref="H18" si="7">SUM(C18:G18)</f>
         <v>850</v>
       </c>
       <c r="I18" s="5">

--- a/MainTop/ink statistic/ink statistic.xlsx
+++ b/MainTop/ink statistic/ink statistic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\ink statistic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAA05967-68BD-4F84-B591-7337CC082DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE71E4F-FF52-4203-8A4D-E93BD54EDB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,8 @@
     <sheet name="остатки 12.05.2026" sheetId="8" r:id="rId7"/>
     <sheet name="Лист8" sheetId="11" r:id="rId8"/>
     <sheet name="остатки" sheetId="10" r:id="rId9"/>
-    <sheet name="спрос" sheetId="12" r:id="rId10"/>
+    <sheet name="Лист6" sheetId="13" r:id="rId10"/>
+    <sheet name="спрос" sheetId="12" r:id="rId11"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="48">
   <si>
     <t>k</t>
   </si>
@@ -284,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -303,9 +304,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -318,6 +316,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -780,6 +784,302 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2AE270E-2E20-42D2-AA0E-D9D45C561DBC}">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="C2" s="5">
+        <v>2</v>
+      </c>
+      <c r="D2" s="22"/>
+      <c r="E2" s="8">
+        <v>7</v>
+      </c>
+      <c r="F2" s="8">
+        <v>6</v>
+      </c>
+      <c r="G2" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="C3" s="5">
+        <v>3</v>
+      </c>
+      <c r="D3" s="22"/>
+      <c r="E3" s="8">
+        <v>7</v>
+      </c>
+      <c r="F3" s="8">
+        <v>6</v>
+      </c>
+      <c r="G3" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0.19</v>
+      </c>
+      <c r="C4" s="5">
+        <v>4</v>
+      </c>
+      <c r="D4" s="22"/>
+      <c r="E4" s="8">
+        <v>15</v>
+      </c>
+      <c r="F4" s="8">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0.24</v>
+      </c>
+      <c r="C5" s="5">
+        <v>7</v>
+      </c>
+      <c r="D5" s="22"/>
+      <c r="E5" s="8">
+        <v>21</v>
+      </c>
+      <c r="F5" s="8">
+        <v>12</v>
+      </c>
+      <c r="G5" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5">
+        <v>2.6</v>
+      </c>
+      <c r="C6" s="5">
+        <v>103</v>
+      </c>
+      <c r="D6" s="22"/>
+      <c r="E6" s="8">
+        <v>130</v>
+      </c>
+      <c r="F6" s="8">
+        <v>126</v>
+      </c>
+      <c r="G6" s="6">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5">
+        <v>4</v>
+      </c>
+      <c r="C7" s="5">
+        <v>140</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8">
+        <v>260</v>
+      </c>
+      <c r="F7" s="23">
+        <v>190</v>
+      </c>
+      <c r="G7" s="19">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="5">
+        <v>1</v>
+      </c>
+      <c r="C8" s="5">
+        <v>88</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="6"/>
+      <c r="G8" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="C9" s="5">
+        <v>25</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="6"/>
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="6"/>
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="5" t="e">
+        <f>#REF!*0.75/24</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C14" s="5">
+        <v>25000</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="5" t="e">
+        <f>#REF!*0.25/24</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C15" s="5">
+        <v>50000</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16">
+        <v>17.850000000000001</v>
+      </c>
+      <c r="C16">
+        <v>610</v>
+      </c>
+      <c r="D16">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29078AD2-6CB5-4717-B063-37BABDC0A719}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -789,7 +1089,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="14">
+      <c r="B1" s="13">
         <v>46179</v>
       </c>
     </row>
@@ -1519,21 +1819,20 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5752FFBB-2BA0-4D25-94B6-08B45A9708D1}">
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" customWidth="1"/>
-    <col min="9" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" customWidth="1"/>
-    <col min="21" max="21" width="12.28515625" customWidth="1"/>
-    <col min="22" max="22" width="11.28515625" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" customWidth="1"/>
+    <col min="18" max="18" width="12.28515625" customWidth="1"/>
+    <col min="19" max="19" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>19</v>
       </c>
@@ -1549,11 +1848,8 @@
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>24000</v>
       </c>
@@ -1569,11 +1865,8 @@
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-    </row>
-    <row r="3" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>23</v>
       </c>
@@ -1584,40 +1877,31 @@
         <v>14</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>30</v>
       </c>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="14" t="s">
+        <v>40</v>
+      </c>
       <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="P3" s="5"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1625,45 +1909,39 @@
         <v>0.09</v>
       </c>
       <c r="C4" s="5">
-        <v>2</v>
-      </c>
-      <c r="E4" s="7">
-        <v>7</v>
-      </c>
-      <c r="F4" s="6">
-        <v>6</v>
-      </c>
-      <c r="G4" s="6">
+        <v>12</v>
+      </c>
+      <c r="D4" s="6">
         <v>8</v>
       </c>
-      <c r="H4" s="1">
-        <f t="shared" ref="H4:H9" si="0">SUM(C4:G4)</f>
-        <v>23</v>
-      </c>
-      <c r="I4" s="5">
+      <c r="E4" s="1">
+        <f>C4+D4</f>
+        <v>20</v>
+      </c>
+      <c r="F4" s="5">
         <f>A2</f>
         <v>24000</v>
       </c>
+      <c r="G4" s="5">
+        <f>ROUNDUP(B4*F4/1000,0)</f>
+        <v>3</v>
+      </c>
+      <c r="H4" s="5">
+        <f t="shared" ref="H4:H12" si="0">ROUNDUP(E4/G4,1)</f>
+        <v>6.6999999999999993</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2</v>
+      </c>
       <c r="J4" s="5">
-        <f t="shared" ref="J4:J12" si="1">ROUNDUP(B4*I4/1000,0)</f>
-        <v>3</v>
-      </c>
-      <c r="K4" s="5">
-        <f t="shared" ref="K4:K12" si="2">ROUNDUP(H4/J4,1)</f>
-        <v>7.6999999999999993</v>
-      </c>
-      <c r="L4" s="5">
-        <v>2</v>
-      </c>
-      <c r="M4" s="5">
-        <f>J4*L4</f>
+        <f>G4*I4</f>
         <v>6</v>
       </c>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
@@ -1671,45 +1949,39 @@
         <v>0.09</v>
       </c>
       <c r="C5" s="5">
-        <v>3</v>
-      </c>
-      <c r="E5" s="7">
-        <v>7</v>
-      </c>
-      <c r="F5" s="6">
         <v>6</v>
       </c>
-      <c r="G5" s="6">
+      <c r="D5" s="6">
         <v>8</v>
       </c>
-      <c r="H5" s="1">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="I5" s="5">
+      <c r="E5" s="1">
+        <f>SUM(C5:D5)</f>
+        <v>14</v>
+      </c>
+      <c r="F5" s="5">
         <f>A2</f>
         <v>24000</v>
       </c>
+      <c r="G5" s="5">
+        <f>ROUNDUP(B5*F5/1000,0)</f>
+        <v>3</v>
+      </c>
+      <c r="H5" s="5">
+        <f t="shared" si="0"/>
+        <v>4.6999999999999993</v>
+      </c>
+      <c r="I5" s="5">
+        <v>2</v>
+      </c>
       <c r="J5" s="5">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K5" s="5">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="L5" s="5">
-        <v>2</v>
-      </c>
-      <c r="M5" s="5">
-        <f t="shared" ref="M5:M12" si="3">J5*L5</f>
+        <f t="shared" ref="J5:J12" si="1">G5*I5</f>
         <v>6</v>
       </c>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
@@ -1717,45 +1989,39 @@
         <v>0.19</v>
       </c>
       <c r="C6" s="5">
-        <v>4</v>
-      </c>
-      <c r="E6" s="7">
-        <v>15</v>
-      </c>
-      <c r="F6" s="6">
+        <v>24</v>
+      </c>
+      <c r="D6" s="6">
         <v>10</v>
       </c>
-      <c r="G6" s="6">
-        <v>10</v>
-      </c>
-      <c r="H6" s="1">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="I6" s="5">
+      <c r="E6" s="1">
+        <f>SUM(C6:D6)</f>
+        <v>34</v>
+      </c>
+      <c r="F6" s="5">
         <f>A2</f>
         <v>24000</v>
       </c>
+      <c r="G6" s="5">
+        <f>ROUNDUP(B6*F6/1000,0)</f>
+        <v>5</v>
+      </c>
+      <c r="H6" s="5">
+        <f t="shared" si="0"/>
+        <v>6.8</v>
+      </c>
+      <c r="I6" s="5">
+        <v>2</v>
+      </c>
       <c r="J6" s="5">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="K6" s="5">
-        <f t="shared" si="2"/>
-        <v>7.8</v>
-      </c>
-      <c r="L6" s="5">
-        <v>2</v>
-      </c>
-      <c r="M6" s="5">
-        <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
@@ -1763,54 +2029,48 @@
         <v>0.24</v>
       </c>
       <c r="C7" s="5">
-        <v>7</v>
-      </c>
-      <c r="E7" s="7">
-        <v>21</v>
-      </c>
-      <c r="F7" s="6">
-        <v>12</v>
-      </c>
-      <c r="G7" s="6">
+        <v>35</v>
+      </c>
+      <c r="D7" s="6">
         <v>8</v>
       </c>
-      <c r="H7" s="1">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-      <c r="I7" s="5">
+      <c r="E7" s="1">
+        <f>SUM(C7:D7)</f>
+        <v>43</v>
+      </c>
+      <c r="F7" s="5">
         <f>A2</f>
         <v>24000</v>
       </c>
+      <c r="G7" s="5">
+        <f>ROUNDUP(B7*F7/1000,0)</f>
+        <v>6</v>
+      </c>
+      <c r="H7" s="5">
+        <f t="shared" si="0"/>
+        <v>7.1999999999999993</v>
+      </c>
+      <c r="I7" s="5">
+        <v>2</v>
+      </c>
       <c r="J7" s="5">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="K7" s="5">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="L7" s="5">
-        <v>2</v>
-      </c>
-      <c r="M7" s="5">
-        <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="T7">
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="Q7">
         <v>1688</v>
       </c>
-      <c r="U7" t="s">
+      <c r="R7" t="s">
         <v>41</v>
       </c>
-      <c r="V7" t="s">
+      <c r="S7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1818,186 +2078,171 @@
         <v>2.6</v>
       </c>
       <c r="C8" s="5">
-        <v>103</v>
-      </c>
-      <c r="E8" s="7">
-        <v>130</v>
-      </c>
-      <c r="F8" s="6">
+        <v>280</v>
+      </c>
+      <c r="D8" s="6">
         <v>126</v>
       </c>
-      <c r="G8" s="6">
-        <v>126</v>
-      </c>
-      <c r="H8" s="1">
-        <f t="shared" si="0"/>
-        <v>485</v>
-      </c>
-      <c r="I8" s="5">
+      <c r="E8" s="1">
+        <f>SUM(C8:D8)</f>
+        <v>406</v>
+      </c>
+      <c r="F8" s="5">
         <f>A2</f>
         <v>24000</v>
       </c>
+      <c r="G8" s="5">
+        <f>ROUNDUP(B8*F8/1000,0)</f>
+        <v>63</v>
+      </c>
+      <c r="H8" s="5">
+        <f t="shared" si="0"/>
+        <v>6.5</v>
+      </c>
+      <c r="I8" s="5">
+        <v>2</v>
+      </c>
       <c r="J8" s="5">
         <f t="shared" si="1"/>
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="K8" s="5">
-        <f t="shared" si="2"/>
-        <v>7.6999999999999993</v>
+        <f>SUM(J4:J8)</f>
+        <v>160</v>
       </c>
       <c r="L8" s="5">
-        <v>2</v>
+        <f>K8*22+K8*3.2*90+950*90</f>
+        <v>135100</v>
       </c>
       <c r="M8" s="5">
-        <f t="shared" si="3"/>
-        <v>126</v>
-      </c>
-      <c r="N8" s="5">
-        <f>SUM(M4:M8)</f>
-        <v>160</v>
-      </c>
-      <c r="O8" s="5">
-        <f>N8*22+N8*3.2*90+950*90</f>
-        <v>135100</v>
-      </c>
-      <c r="P8" s="5">
-        <f>O8*2</f>
+        <f>L8*2</f>
         <v>270200</v>
       </c>
-      <c r="R8">
-        <f>950+M9*5</f>
+      <c r="O8">
+        <f>950+J9*5</f>
         <v>1910</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="5">
         <v>4</v>
       </c>
       <c r="C9" s="5">
-        <v>140</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8">
-        <v>260</v>
-      </c>
-      <c r="F9" s="20">
+        <v>510</v>
+      </c>
+      <c r="D9" s="19">
         <v>190</v>
       </c>
-      <c r="G9" s="20">
-        <v>190</v>
-      </c>
-      <c r="H9" s="1">
-        <f t="shared" si="0"/>
-        <v>780</v>
-      </c>
-      <c r="I9" s="5">
+      <c r="E9" s="1">
+        <f>SUM(C9:D9)</f>
+        <v>700</v>
+      </c>
+      <c r="F9" s="5">
         <f>A2</f>
         <v>24000</v>
       </c>
+      <c r="G9" s="5">
+        <f>ROUNDUP(B9*F9/1000,0)</f>
+        <v>96</v>
+      </c>
+      <c r="H9" s="5">
+        <f t="shared" si="0"/>
+        <v>7.3</v>
+      </c>
+      <c r="I9" s="5">
+        <v>2</v>
+      </c>
       <c r="J9" s="5">
         <f t="shared" si="1"/>
-        <v>96</v>
-      </c>
-      <c r="K9" s="5">
-        <f t="shared" si="2"/>
-        <v>8.1999999999999993</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="K9" s="5"/>
       <c r="L9" s="5">
-        <v>2</v>
+        <f>J9*3.2*90+J9*22</f>
+        <v>59520.000000000007</v>
       </c>
       <c r="M9" s="5">
-        <f t="shared" si="3"/>
-        <v>192</v>
-      </c>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5">
-        <f>M9*3.2*90+M9*22</f>
-        <v>59520.000000000007</v>
-      </c>
-      <c r="P9" s="5">
-        <f>O9*2</f>
+        <f>L9*2</f>
         <v>119040.00000000001</v>
       </c>
-      <c r="T9">
+      <c r="Q9">
         <f>(3.48+3.2)*90+22</f>
         <v>623.19999999999993</v>
       </c>
-      <c r="U9">
+      <c r="R9">
         <f>8.2*90+1*22</f>
         <v>759.99999999999989</v>
       </c>
-      <c r="V9">
+      <c r="S9">
         <v>930</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="5">
         <v>1</v>
       </c>
       <c r="C10" s="5">
-        <v>88</v>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="6"/>
-      <c r="G10" s="6">
+        <v>58</v>
+      </c>
+      <c r="D10" s="6">
         <v>100</v>
       </c>
-      <c r="H10" s="1">
-        <f t="shared" ref="H10:H17" si="4">SUM(C10:G10)</f>
-        <v>188</v>
-      </c>
-      <c r="I10" s="5">
+      <c r="E10" s="1">
+        <f>SUM(C10:D10)</f>
+        <v>158</v>
+      </c>
+      <c r="F10" s="5">
         <f>A2</f>
         <v>24000</v>
       </c>
+      <c r="G10" s="5">
+        <f>ROUNDUP(B10*F10/1000,0)</f>
+        <v>24</v>
+      </c>
+      <c r="H10" s="5">
+        <f t="shared" si="0"/>
+        <v>6.6</v>
+      </c>
+      <c r="I10" s="5">
+        <v>2</v>
+      </c>
       <c r="J10" s="5">
         <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-      <c r="K10" s="5">
-        <f t="shared" si="2"/>
-        <v>7.8999999999999995</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="K10" s="5"/>
       <c r="L10" s="5">
-        <v>2</v>
+        <f>J10*3800+J10*22</f>
+        <v>183456</v>
       </c>
       <c r="M10" s="5">
-        <f t="shared" si="3"/>
-        <v>48</v>
-      </c>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5">
-        <f>M10*3800+M10*22</f>
-        <v>183456</v>
-      </c>
-      <c r="P10" s="5">
         <f>100*3600+100*22</f>
         <v>362200</v>
       </c>
-      <c r="S10" s="5">
+      <c r="P10" s="5">
         <v>192</v>
       </c>
-      <c r="T10">
-        <f>T9*S10</f>
+      <c r="Q10">
+        <f>Q9*P10</f>
         <v>119654.39999999999</v>
       </c>
-      <c r="U10">
-        <f>U9*S10</f>
+      <c r="R10">
+        <f>R9*P10</f>
         <v>145919.99999999997</v>
       </c>
-      <c r="V10">
-        <f>V9*S10</f>
+      <c r="S10">
+        <f>S9*P10</f>
         <v>178560</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="5">
@@ -2007,42 +2252,40 @@
         <v>25</v>
       </c>
       <c r="D11" s="7"/>
-      <c r="E11" s="6"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="1">
-        <f t="shared" si="4"/>
+      <c r="E11" s="1">
+        <f>SUM(C11:D11)</f>
         <v>25</v>
       </c>
-      <c r="I11" s="5">
+      <c r="F11" s="5">
         <f>A2</f>
         <v>24000</v>
       </c>
+      <c r="G11" s="5">
+        <f>ROUNDUP(B11*F11/1000,0)</f>
+        <v>6</v>
+      </c>
+      <c r="H11" s="5">
+        <f t="shared" si="0"/>
+        <v>4.1999999999999993</v>
+      </c>
+      <c r="I11" s="5">
+        <v>2</v>
+      </c>
       <c r="J11" s="5">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="K11" s="5">
-        <f t="shared" si="2"/>
-        <v>4.1999999999999993</v>
-      </c>
-      <c r="L11" s="5">
-        <v>2</v>
-      </c>
-      <c r="M11" s="5">
-        <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="N11" s="5"/>
-      <c r="O11" s="19">
-        <f>SUM(O8:O10)</f>
+      <c r="K11" s="5"/>
+      <c r="L11" s="18">
+        <f>SUM(L8:L10)</f>
         <v>378076</v>
       </c>
-      <c r="P11" s="19">
-        <f>SUM(P8:P10)</f>
+      <c r="M11" s="18">
+        <f>SUM(M8:M10)</f>
         <v>751440</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>13</v>
       </c>
@@ -2053,115 +2296,104 @@
         <v>2</v>
       </c>
       <c r="D12" s="7"/>
-      <c r="E12" s="6"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="1">
-        <f t="shared" si="4"/>
+      <c r="E12" s="1">
+        <f>SUM(C12:D12)</f>
         <v>2</v>
       </c>
-      <c r="I12" s="5">
+      <c r="F12" s="5">
         <f>A2</f>
         <v>24000</v>
       </c>
+      <c r="G12" s="5">
+        <f>ROUNDUP(B12*F12/1000,0)</f>
+        <v>6</v>
+      </c>
+      <c r="H12" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="I12" s="5">
+        <v>2</v>
+      </c>
       <c r="J12" s="5">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="K12" s="5">
-        <f t="shared" si="2"/>
-        <v>0.4</v>
-      </c>
-      <c r="L12" s="5">
-        <v>2</v>
-      </c>
-      <c r="M12" s="5">
-        <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
         <v>24</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
+      <c r="E13" s="1">
+        <f>SUM(C13:D13)</f>
+        <v>0</v>
+      </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="1">
-        <f t="shared" si="4"/>
+      <c r="G13" s="5">
+        <f>ROUNDUP(B13*F13/1000,0)</f>
         <v>0</v>
       </c>
+      <c r="H13" s="5"/>
       <c r="I13" s="5"/>
-      <c r="J13" s="5">
-        <f t="shared" ref="J13:J17" si="5">ROUNDUP(B13*I13/1000,0)</f>
-        <v>0</v>
-      </c>
+      <c r="J13" s="5"/>
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
         <v>28</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
+      <c r="E14" s="1">
+        <f>SUM(C14:D14)</f>
+        <v>0</v>
+      </c>
       <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="1">
-        <f t="shared" si="4"/>
+      <c r="G14" s="5">
+        <f>ROUNDUP(B14*F14/1000,0)</f>
         <v>0</v>
       </c>
+      <c r="H14" s="5"/>
       <c r="I14" s="5"/>
-      <c r="J14" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="J14" s="5"/>
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
+      <c r="E15" s="1">
+        <f>SUM(C15:D15)</f>
+        <v>0</v>
+      </c>
       <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="1">
-        <f t="shared" si="4"/>
+      <c r="G15" s="5">
+        <f>ROUNDUP(B15*F15/1000,0)</f>
         <v>0</v>
       </c>
+      <c r="H15" s="5"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="J15" s="5"/>
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
         <v>25</v>
       </c>
       <c r="B16" s="5">
@@ -2172,33 +2404,30 @@
         <v>25000</v>
       </c>
       <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="1">
-        <f t="shared" si="4"/>
+      <c r="E16" s="1">
+        <f>SUM(C16:D16)</f>
         <v>25000</v>
       </c>
-      <c r="I16" s="5">
+      <c r="F16" s="5">
         <f>A2</f>
         <v>24000</v>
       </c>
-      <c r="J16" s="5">
-        <f t="shared" si="5"/>
+      <c r="G16" s="5">
+        <f>ROUNDUP(B16*F16/1000,0)</f>
         <v>18000</v>
       </c>
-      <c r="K16" s="5">
-        <f t="shared" ref="K16:K17" si="6">ROUNDUP(H16/J16,1)</f>
+      <c r="H16" s="5">
+        <f t="shared" ref="H16:H17" si="2">ROUNDUP(E16/G16,1)</f>
         <v>1.4000000000000001</v>
       </c>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
         <v>26</v>
       </c>
       <c r="B17" s="5">
@@ -2209,33 +2438,30 @@
         <v>50000</v>
       </c>
       <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="1">
-        <f t="shared" si="4"/>
+      <c r="E17" s="1">
+        <f>SUM(C17:D17)</f>
         <v>50000</v>
       </c>
-      <c r="I17" s="5">
+      <c r="F17" s="5">
         <f>A2</f>
         <v>24000</v>
       </c>
-      <c r="J17" s="5">
-        <f t="shared" si="5"/>
+      <c r="G17" s="5">
+        <f>ROUNDUP(B17*F17/1000,0)</f>
         <v>6000</v>
       </c>
-      <c r="K17" s="5">
-        <f t="shared" si="6"/>
+      <c r="H17" s="5">
+        <f t="shared" si="2"/>
         <v>8.4</v>
       </c>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>46</v>
       </c>
       <c r="B18">
@@ -2247,37 +2473,37 @@
       <c r="D18">
         <v>240</v>
       </c>
-      <c r="H18" s="1">
-        <f t="shared" ref="H18" si="7">SUM(C18:G18)</f>
+      <c r="E18" s="1">
+        <f>SUM(C18:D18)</f>
         <v>850</v>
       </c>
-      <c r="I18" s="5">
+      <c r="F18" s="5">
         <f>A2</f>
         <v>24000</v>
       </c>
+      <c r="G18" s="5">
+        <f>ROUNDUP(B18*F18/1000,0)</f>
+        <v>429</v>
+      </c>
+      <c r="H18" s="5">
+        <f>ROUNDUP(E18/G18,1)</f>
+        <v>2</v>
+      </c>
+      <c r="I18" s="5">
+        <v>2</v>
+      </c>
       <c r="J18" s="5">
-        <f>ROUNDUP(B18*I18/1000,0)</f>
-        <v>429</v>
-      </c>
-      <c r="K18" s="5">
-        <f>ROUNDUP(H18/J18,1)</f>
-        <v>2</v>
-      </c>
-      <c r="L18" s="5">
-        <v>2</v>
-      </c>
-      <c r="M18" s="5">
-        <f>J18*L18</f>
+        <f>G18*I18</f>
         <v>858</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="17" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="17" t="s">
         <v>45</v>
       </c>
     </row>
